--- a/schema/domain-config.xlsx
+++ b/schema/domain-config.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实体类型" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关联关系" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方案章节结构(预留v4)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="实体类型" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="字段清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="关联关系" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="方案章节结构(预留v4)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Experience Types" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Experience Section Types" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -90,7 +92,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -112,11 +114,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -142,6 +188,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -921,6 +969,12 @@
           <t>【通用】</t>
         </is>
       </c>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="10" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -1233,6 +1287,12 @@
           <t>【客户案例】</t>
         </is>
       </c>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="10" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -1532,6 +1592,12 @@
           <t>【政策文件】</t>
         </is>
       </c>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="10" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -1675,6 +1741,12 @@
           <t>【证书专利】</t>
         </is>
       </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="10" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
@@ -1818,6 +1890,12 @@
           <t>【竞品画像】</t>
         </is>
       </c>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="10" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -2664,4 +2742,416 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>subtypeName</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>subtype_abbr</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>triggerCondition</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>coreDimensions</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>applicableSections</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>jiedai-session</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Each reception event completed</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>theme_packages/module_ids/client_tier/attendee_count</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>visitor-insights/narration-record/qa-record</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Full record of a single reception event</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>monthly-report</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Monthly recurring</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>period/key_metrics/highlights</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>data-summary/trend-analysis</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Monthly operations summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>lesson-record</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lesson</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Manual trigger</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>applicable_scenarios/issue_type/modules</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lesson/recommendation</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Patterns and insights from multiple events</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sectionTag</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>meaning</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sourceMethod</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>applicableSubtype</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>enrichTarget</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>enrichField</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>visitor-insights</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Visitor focus, interests and reactions</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Audio analysis / human observation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>enrichC-&gt;schema-suggestions</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>schema-suggestions.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>narration-record</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Actual narration scripts (not planned scripts)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Audio transcription</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>enrichB-&gt;narration append</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[narration] section</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>qa-record</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Real Q&amp;A on-site (actual questions + actual answers)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Audio analysis / human record</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>enrichA-&gt;qa append</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[qa] section</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>data-summary</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Data aggregation and key metrics</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>System export / manual</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>trend-analysis</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Trend analysis and period comparison</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Manual analysis</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lesson</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lessons learned and patterns</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Manual curation</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>lesson</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Action recommendations based on lessons</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Manual curation</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>lesson</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>